--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-09-29 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:03</t>
+    <t xml:space="preserve">2026-09-29 18:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:36</t>
+    <t xml:space="preserve">2026-10-05 04:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -507,10 +507,10 @@
         <v>5.63</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>33.26</v>
+        <v>33.27</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>27.63</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="4">
@@ -538,7 +538,7 @@
         <v>27.7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
     </row>
   </sheetData>
